--- a/factory/兔司家门店商品月度销售报表_格式化模板.xlsx
+++ b/factory/兔司家门店商品月度销售报表_格式化模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B584A683-772C-46D3-8CD4-43CA63525D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDD40F5-494D-4937-BF67-A8273D99B60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="833" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,7 +188,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -280,13 +280,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -489,6 +482,48 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -498,45 +533,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,14 +542,11 @@
     <xf numFmtId="176" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1064,23 +1059,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="5" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
     </row>
@@ -1132,10 +1127,10 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="22.05" customHeight="1">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="23"/>
+      <c r="B3" s="37"/>
       <c r="C3" s="13">
         <f t="shared" ref="C3:O3" si="0">SUM(C4:C5)</f>
         <v>0</v>
@@ -1196,10 +1191,16 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
+      <c r="D4" s="13">
+        <f>C4-F4</f>
+        <v>0</v>
+      </c>
       <c r="E4" s="14"/>
       <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="G4" s="15">
+        <f>C4-F4-H4</f>
+        <v>0</v>
+      </c>
       <c r="H4" s="15"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
@@ -1216,10 +1217,16 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
+      <c r="D5" s="13">
+        <f t="shared" ref="D5" si="2">C5-F5</f>
+        <v>0</v>
+      </c>
       <c r="E5" s="14"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="G5" s="15">
+        <f>C5-F5-H5</f>
+        <v>0</v>
+      </c>
       <c r="H5" s="15"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
@@ -1276,249 +1283,249 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="4" customFormat="1" ht="25.05" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="41"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="41"/>
     </row>
     <row r="2" spans="1:26" ht="19.95" customHeight="1">
-      <c r="A2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="34"/>
-      <c r="I2" s="24" t="s">
+      <c r="H2" s="39"/>
+      <c r="I2" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="34"/>
-      <c r="K2" s="24" t="s">
+      <c r="J2" s="39"/>
+      <c r="K2" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="34"/>
-      <c r="M2" s="24" t="s">
+      <c r="L2" s="39"/>
+      <c r="M2" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="34"/>
-      <c r="O2" s="24" t="s">
+      <c r="N2" s="39"/>
+      <c r="O2" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="24" t="s">
+      <c r="P2" s="39"/>
+      <c r="Q2" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="R2" s="34"/>
-      <c r="S2" s="24" t="s">
+      <c r="R2" s="39"/>
+      <c r="S2" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="T2" s="34"/>
-      <c r="U2" s="24" t="s">
+      <c r="T2" s="39"/>
+      <c r="U2" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="34"/>
-      <c r="W2" s="24" t="s">
+      <c r="V2" s="39"/>
+      <c r="W2" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="24" t="s">
+      <c r="X2" s="39"/>
+      <c r="Y2" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="Z2" s="34"/>
+      <c r="Z2" s="39"/>
     </row>
     <row r="3" spans="1:26" ht="19.95" customHeight="1">
-      <c r="A3" s="22"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="25" t="s">
+      <c r="A3" s="36"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="M3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="27" t="s">
+      <c r="N3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="27" t="s">
+      <c r="P3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="Q3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="R3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="25" t="s">
+      <c r="S3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="27" t="s">
+      <c r="T3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="U3" s="25" t="s">
+      <c r="U3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="27" t="s">
+      <c r="V3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="W3" s="25" t="s">
+      <c r="W3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="X3" s="27" t="s">
+      <c r="X3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="25" t="s">
+      <c r="Y3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="27" t="s">
+      <c r="Z3" s="22" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:26" customFormat="1" ht="19.95" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="25">
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="20">
         <f t="shared" ref="G4:Z4" si="0">SUM(G5:G7)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J4" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L4" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N4" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P4" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R4" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T4" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V4" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X4" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="27">
+      <c r="H4" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X4" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1537,28 +1544,28 @@
         <f t="shared" ref="G5:H7" si="2">SUM(I5,K5,M5,O5,Q5,S5,U5,W5,Y5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I5" s="12"/>
-      <c r="J5" s="33"/>
+      <c r="J5" s="28"/>
       <c r="K5" s="12"/>
-      <c r="L5" s="33"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="12"/>
-      <c r="N5" s="33"/>
+      <c r="N5" s="28"/>
       <c r="O5" s="12"/>
-      <c r="P5" s="33"/>
+      <c r="P5" s="28"/>
       <c r="Q5" s="12"/>
-      <c r="R5" s="33"/>
+      <c r="R5" s="28"/>
       <c r="S5" s="12"/>
-      <c r="T5" s="33"/>
+      <c r="T5" s="28"/>
       <c r="U5" s="12"/>
-      <c r="V5" s="33"/>
+      <c r="V5" s="28"/>
       <c r="W5" s="12"/>
-      <c r="X5" s="33"/>
+      <c r="X5" s="28"/>
       <c r="Y5" s="12"/>
-      <c r="Z5" s="33"/>
+      <c r="Z5" s="28"/>
     </row>
     <row r="6" spans="1:26" ht="19.95" customHeight="1">
       <c r="A6" s="12">
@@ -1574,28 +1581,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I6" s="12"/>
-      <c r="J6" s="33"/>
+      <c r="J6" s="28"/>
       <c r="K6" s="12"/>
-      <c r="L6" s="33"/>
+      <c r="L6" s="28"/>
       <c r="M6" s="12"/>
-      <c r="N6" s="33"/>
+      <c r="N6" s="28"/>
       <c r="O6" s="12"/>
-      <c r="P6" s="33"/>
+      <c r="P6" s="28"/>
       <c r="Q6" s="12"/>
-      <c r="R6" s="33"/>
+      <c r="R6" s="28"/>
       <c r="S6" s="12"/>
-      <c r="T6" s="33"/>
+      <c r="T6" s="28"/>
       <c r="U6" s="12"/>
-      <c r="V6" s="33"/>
+      <c r="V6" s="28"/>
       <c r="W6" s="12"/>
-      <c r="X6" s="33"/>
+      <c r="X6" s="28"/>
       <c r="Y6" s="12"/>
-      <c r="Z6" s="33"/>
+      <c r="Z6" s="28"/>
     </row>
     <row r="7" spans="1:26" ht="19.95" customHeight="1">
       <c r="A7" s="12">
@@ -1611,28 +1618,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I7" s="12"/>
-      <c r="J7" s="33"/>
+      <c r="J7" s="28"/>
       <c r="K7" s="12"/>
-      <c r="L7" s="33"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="12"/>
-      <c r="N7" s="33"/>
+      <c r="N7" s="28"/>
       <c r="O7" s="12"/>
-      <c r="P7" s="33"/>
+      <c r="P7" s="28"/>
       <c r="Q7" s="12"/>
-      <c r="R7" s="33"/>
+      <c r="R7" s="28"/>
       <c r="S7" s="12"/>
-      <c r="T7" s="33"/>
+      <c r="T7" s="28"/>
       <c r="U7" s="12"/>
-      <c r="V7" s="33"/>
+      <c r="V7" s="28"/>
       <c r="W7" s="12"/>
-      <c r="X7" s="33"/>
+      <c r="X7" s="28"/>
       <c r="Y7" s="12"/>
-      <c r="Z7" s="33"/>
+      <c r="Z7" s="28"/>
     </row>
     <row r="8" spans="1:26" ht="19.95" customHeight="1"/>
   </sheetData>
@@ -1640,6 +1647,8 @@
     <sortCondition descending="1" ref="C2"/>
   </sortState>
   <mergeCells count="17">
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="O2:P2"/>
@@ -1655,8 +1664,6 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="S2:T2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1681,58 +1688,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8 16335:16335" ht="24" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="41"/>
       <c r="XDG1" s="1"/>
     </row>
     <row r="2" spans="1:8 16335:16335" ht="19.95" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8 16335:16335" customFormat="1" ht="19.95" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="25">
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="20">
         <f>SUM(G4:G6)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="21">
         <f>SUM(H4:H6)</f>
         <v>0</v>
       </c>
@@ -1743,12 +1750,12 @@
         <v>1</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="31"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
-      <c r="H4" s="32"/>
+      <c r="H4" s="27"/>
     </row>
     <row r="5" spans="1:8 16335:16335" ht="19.95" customHeight="1">
       <c r="A5" s="12">
@@ -1761,7 +1768,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
-      <c r="H5" s="32"/>
+      <c r="H5" s="27"/>
     </row>
     <row r="6" spans="1:8 16335:16335" ht="19.95" customHeight="1">
       <c r="A6" s="12">
@@ -1774,7 +1781,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="32"/>
+      <c r="H6" s="27"/>
       <c r="XDG6" s="1"/>
     </row>
     <row r="7" spans="1:8 16335:16335" ht="19.95" customHeight="1">
